--- a/Reports/Summary_Report.xlsx
+++ b/Reports/Summary_Report.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.54000000000001</v>
+        <v>76.23</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
